--- a/小鸭/美妆戴森电玩行情日更临时表.xlsx
+++ b/小鸭/美妆戴森电玩行情日更临时表.xlsx
@@ -29,19 +29,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
-  <si>
-    <t>673/24年</t>
-  </si>
-  <si>
-    <t>585/24年</t>
-  </si>
-  <si>
-    <t>605/24年</t>
-  </si>
-  <si>
-    <r>
-      <t>178/英文</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+  <si>
+    <r>
+      <t>690-25年</t>
     </r>
     <r>
       <rPr>
@@ -62,15 +53,24 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>180/中文</t>
-    </r>
-  </si>
-  <si>
-    <t>935/24年</t>
-  </si>
-  <si>
-    <r>
-      <t>2300-24下</t>
+      <t>690-光子</t>
+    </r>
+  </si>
+  <si>
+    <t>590-25年</t>
+  </si>
+  <si>
+    <t>635光子</t>
+  </si>
+  <si>
+    <t>167-25年</t>
+  </si>
+  <si>
+    <t>165-25年</t>
+  </si>
+  <si>
+    <r>
+      <t>180/183英文</t>
     </r>
     <r>
       <rPr>
@@ -91,12 +91,12 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2280-24上</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>564-150ml</t>
+      <t>182/183中文</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>283有标</t>
     </r>
     <r>
       <rPr>
@@ -117,15 +117,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>702-200ml</t>
-    </r>
-  </si>
-  <si>
-    <t>564/ 735</t>
-  </si>
-  <si>
-    <r>
-      <t>803</t>
+      <t>288无标</t>
     </r>
     <r>
       <rPr>
@@ -146,15 +138,21 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>510-50ML</t>
-    </r>
-  </si>
-  <si>
-    <t>376-24年</t>
-  </si>
-  <si>
-    <r>
-      <t>209-125ml</t>
+      <t>300新版七代</t>
+    </r>
+  </si>
+  <si>
+    <t>1170-25年</t>
+  </si>
+  <si>
+    <t>临期1370</t>
+  </si>
+  <si>
+    <t>605-150ml</t>
+  </si>
+  <si>
+    <r>
+      <t>805</t>
     </r>
     <r>
       <rPr>
@@ -175,15 +173,12 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>111-50ml</t>
-    </r>
-  </si>
-  <si>
-    <t>124-250ml</t>
-  </si>
-  <si>
-    <r>
-      <t>377</t>
+      <t>800日版</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>663-25年</t>
     </r>
     <r>
       <rPr>
@@ -204,27 +199,15 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>340无盒</t>
-    </r>
-  </si>
-  <si>
-    <t>422九代-24年</t>
-  </si>
-  <si>
-    <t>527九代-24年</t>
-  </si>
-  <si>
-    <t>720九代</t>
-  </si>
-  <si>
-    <t>608新版</t>
-  </si>
-  <si>
-    <t>645新版</t>
-  </si>
-  <si>
-    <r>
-      <t>400-24年</t>
+      <t>653-24年</t>
+    </r>
+  </si>
+  <si>
+    <t>471-24年上</t>
+  </si>
+  <si>
+    <r>
+      <t>204-25年</t>
     </r>
     <r>
       <rPr>
@@ -245,21 +228,12 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>380四代</t>
-    </r>
-  </si>
-  <si>
-    <t>三代100ml500</t>
-  </si>
-  <si>
-    <t>196-24年</t>
-  </si>
-  <si>
-    <t>/ 73</t>
-  </si>
-  <si>
-    <r>
-      <t>592新版</t>
+      <t>198-24年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>127-中文</t>
     </r>
     <r>
       <rPr>
@@ -280,30 +254,18 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>588老版</t>
-    </r>
-  </si>
-  <si>
-    <t>420/24年</t>
-  </si>
-  <si>
-    <t>435/24年</t>
-  </si>
-  <si>
-    <t>94 /</t>
-  </si>
-  <si>
-    <t>166-24年</t>
-  </si>
-  <si>
-    <t>313-200ml</t>
-  </si>
-  <si>
-    <t>337-200ml</t>
-  </si>
-  <si>
-    <r>
-      <t>532-24年</t>
+      <t>130-英文</t>
+    </r>
+  </si>
+  <si>
+    <t>204-25年</t>
+  </si>
+  <si>
+    <t>750-25年</t>
+  </si>
+  <si>
+    <r>
+      <t>422-50m清爽</t>
     </r>
     <r>
       <rPr>
@@ -324,18 +286,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>525-23年</t>
-    </r>
-  </si>
-  <si>
-    <t>/ 164</t>
-  </si>
-  <si>
-    <t>210滋润</t>
-  </si>
-  <si>
-    <r>
-      <t>428-24年浓</t>
+      <t>590-75m清爽</t>
     </r>
     <r>
       <rPr>
@@ -356,19 +307,31 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>550-90ml</t>
-    </r>
-  </si>
-  <si>
-    <t>223-30ml</t>
-  </si>
-  <si>
-    <r>
-      <t>345淡-100ml</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+      <t>710-100m清爽</t>
+    </r>
+  </si>
+  <si>
+    <t>217新版</t>
+  </si>
+  <si>
+    <t>144-25年</t>
+  </si>
+  <si>
+    <t>570新版</t>
+  </si>
+  <si>
+    <t>395-25年</t>
+  </si>
+  <si>
+    <t>三代532-25年</t>
+  </si>
+  <si>
+    <r>
+      <t>214-25年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -379,31 +342,37 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>256淡-50ml</t>
-    </r>
-  </si>
-  <si>
-    <t>169-30ml</t>
-  </si>
-  <si>
-    <t>415淡-100ml</t>
-  </si>
-  <si>
-    <t>351-24年</t>
-  </si>
-  <si>
-    <r>
-      <t>固反837</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>204-24年下</t>
+    </r>
+  </si>
+  <si>
+    <t>413固</t>
+  </si>
+  <si>
+    <t>190PO-01</t>
+  </si>
+  <si>
+    <t>168-25年</t>
+  </si>
+  <si>
+    <t>645新版</t>
+  </si>
+  <si>
+    <t>415-25年</t>
+  </si>
+  <si>
+    <r>
+      <t>242</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -414,22 +383,31 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>787+50</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>固反1032</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>177-1W2</t>
+    </r>
+  </si>
+  <si>
+    <t>328-200ml</t>
+  </si>
+  <si>
+    <t>325-200ml</t>
+  </si>
+  <si>
+    <t>230-25年</t>
+  </si>
+  <si>
+    <r>
+      <t>540-25年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -440,22 +418,17 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>997+35</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>固反992</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>499-24年下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -466,22 +439,56 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>957+35</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>固反1234</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>470-24年上</t>
+    </r>
+  </si>
+  <si>
+    <t>58/新版</t>
+  </si>
+  <si>
+    <t>685天率丹</t>
+  </si>
+  <si>
+    <t>101 /</t>
+  </si>
+  <si>
+    <r>
+      <t>86 /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>165</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>455-50ML浓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -492,22 +499,47 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1199+35</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>固反1096</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>560-90ml浓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>353/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>361-100ml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -518,32 +550,242 @@
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>260-50ml</t>
+    </r>
+  </si>
+  <si>
+    <t>373-50ml</t>
+  </si>
+  <si>
+    <r>
+      <t>183-30ml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>235-50ml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>285-90ml</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>181-50ml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>260-100ml</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>305-50ml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>400-100ml淡</t>
+    </r>
+  </si>
+  <si>
+    <t>94-200ml</t>
+  </si>
+  <si>
+    <r>
+      <t>1890-30ml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>1061+35</t>
-    </r>
-  </si>
-  <si>
-    <t>5030/ 4520</t>
-  </si>
-  <si>
-    <t>2630/ 3290</t>
+      <t>2770-50ml调价</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1330-20ml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2410-50ml</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3270-港版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3210-新加坡版</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3580-港版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3520-新加坡版</t>
+    </r>
+  </si>
+  <si>
+    <t>5900/ 5700</t>
+  </si>
+  <si>
+    <t>2470/ 3070</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="177" formatCode="#\ ???/???"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -570,14 +812,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -728,7 +970,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -749,12 +991,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF88825"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -940,7 +1176,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -955,6 +1191,19 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -980,10 +1229,10 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -993,35 +1242,11 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1159,7 +1384,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1171,204 +1396,192 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1682,1013 +1895,1041 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A246"/>
+  <dimension ref="A1:A248"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1">
-        <v>46030</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" ht="27" spans="1:1">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4">
-        <v>928</v>
+      <c r="A4" s="3">
+        <v>930</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4"/>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4"/>
+      <c r="A8" s="3"/>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5">
-        <v>1270</v>
+      <c r="A9" s="4">
+        <v>1353</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4">
-        <v>375</v>
+      <c r="A10" s="3">
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="4"/>
+      <c r="A11" s="3"/>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4"/>
+      <c r="A12" s="3"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4"/>
+      <c r="A13" s="4">
+        <v>213</v>
+      </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4">
+        <v>227</v>
+      </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4"/>
+      <c r="A15" s="3"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5">
-        <v>214</v>
-      </c>
+      <c r="A16" s="5"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5">
-        <v>230</v>
+      <c r="A17" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="6"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="4">
-        <v>169</v>
+      <c r="A18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" ht="54" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" ht="27" spans="1:1">
-      <c r="A21" s="4" t="s">
-        <v>3</v>
+      <c r="A20" s="5"/>
+    </row>
+    <row r="21" ht="54" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="6"/>
+      <c r="A22" s="3"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="4"/>
+      <c r="A23" s="5"/>
+    </row>
+    <row r="24" ht="27" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="6"/>
+      <c r="A25" s="3">
+        <v>660</v>
+      </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
-        <v>4</v>
+      <c r="A26" s="6">
+        <v>485</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="4">
-        <v>705</v>
+        <v>671</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="7">
-        <v>490</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="5">
-        <v>625</v>
+      <c r="A29" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="8">
-        <v>2475</v>
-      </c>
-    </row>
-    <row r="31" ht="54" spans="1:1">
-      <c r="A31" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="A30" s="3"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="3"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4">
-        <v>1510</v>
+      <c r="A32" s="8">
+        <v>1800</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4">
-        <v>1045</v>
+      <c r="A33" s="8">
+        <v>3050</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="8"/>
+      <c r="A34" s="3"/>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="8">
-        <v>285</v>
-      </c>
+      <c r="A35" s="9"/>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="8"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="9"/>
+      <c r="A37" s="8"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="3"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="6"/>
-    </row>
-    <row r="41" ht="54" spans="1:1">
-      <c r="A41" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" ht="27" spans="1:1">
-      <c r="A43" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="4">
-        <v>350</v>
+      <c r="A39" s="5"/>
+    </row>
+    <row r="40" ht="27" spans="1:1">
+      <c r="A40" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" ht="27" spans="1:1">
+      <c r="A42" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="4">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="44" ht="27" spans="1:1">
+      <c r="A44" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="4">
-        <v>670</v>
-      </c>
+      <c r="A45" s="3"/>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="4">
-        <v>615</v>
-      </c>
+      <c r="A46" s="3"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="4">
-        <v>1190</v>
-      </c>
+      <c r="A47" s="3"/>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="4">
-        <v>1710</v>
-      </c>
+      <c r="A48" s="3"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="6"/>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" ht="40.5" spans="1:1">
-      <c r="A51" s="4" t="s">
-        <v>10</v>
+      <c r="A49" s="5"/>
+    </row>
+    <row r="50" ht="27" spans="1:1">
+      <c r="A50" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" ht="27" spans="1:1">
+      <c r="A51" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="4"/>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="4"/>
+      <c r="A52" s="3"/>
+    </row>
+    <row r="53" ht="27" spans="1:1">
+      <c r="A53" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="4">
-        <v>130</v>
+      <c r="A54" s="3">
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="4">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="56" ht="27" spans="1:1">
-      <c r="A56" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="A55" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="3"/>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="5">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="58" ht="27" spans="1:1">
-      <c r="A58" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="A57" s="4"/>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="3"/>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="6"/>
-    </row>
-    <row r="60" ht="27" spans="1:1">
-      <c r="A60" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" ht="27" spans="1:1">
-      <c r="A61" s="4" t="s">
-        <v>14</v>
+      <c r="A59" s="3"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="5"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="3">
+        <v>452</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="4" t="s">
-        <v>15</v>
+      <c r="A62" s="3">
+        <v>590</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="4"/>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="4"/>
+      <c r="A63" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" ht="81" spans="1:1">
+      <c r="A64" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="4">
-        <v>228</v>
-      </c>
+      <c r="A65" s="3"/>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="4">
-        <v>185</v>
-      </c>
+      <c r="A66" s="3"/>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="4">
-        <v>127</v>
+      <c r="A67" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="4" t="s">
-        <v>16</v>
+      <c r="A68" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="4" t="s">
-        <v>17</v>
+      <c r="A69" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="10"/>
+      <c r="A70" s="3">
+        <v>810</v>
+      </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="4">
-        <v>800</v>
+      <c r="A71" s="3">
+        <v>785</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="4"/>
+      <c r="A72" s="3">
+        <v>1235</v>
+      </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="4"/>
+      <c r="A73" s="3"/>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="6"/>
+      <c r="A74" s="5"/>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="4"/>
-    </row>
-    <row r="76" ht="27" spans="1:1">
-      <c r="A76" s="4" t="s">
-        <v>18</v>
+      <c r="A75" s="3"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="3">
+        <v>423</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="4"/>
+      <c r="A77" s="3"/>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="4">
-        <v>245</v>
+      <c r="A78" s="3">
+        <v>221</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="4">
-        <v>362</v>
+      <c r="A79" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="6"/>
+      <c r="A80" s="5"/>
     </row>
     <row r="81" ht="27" spans="1:1">
-      <c r="A81" s="4" t="s">
-        <v>19</v>
+      <c r="A81" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="4">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="4" t="s">
-        <v>20</v>
+      <c r="A82" s="3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="83" ht="40.5" spans="1:1">
+      <c r="A83" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="4"/>
+      <c r="A84" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="4"/>
+      <c r="A85" s="3"/>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="4"/>
+      <c r="A86" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="4"/>
+      <c r="A87" s="3">
+        <v>900</v>
+      </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="4">
-        <v>165</v>
+      <c r="A88" s="3">
+        <v>483</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="4"/>
+      <c r="A89" s="3"/>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="4"/>
+      <c r="A90" s="5"/>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="11"/>
+      <c r="A91" s="3">
+        <v>225</v>
+      </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="6"/>
+      <c r="A92" s="3">
+        <v>368</v>
+      </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="4">
-        <v>221</v>
+      <c r="A93" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="4">
-        <v>348</v>
+      <c r="A94" s="3">
+        <v>276</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="4">
-        <v>160</v>
-      </c>
+      <c r="A95" s="10"/>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="4">
-        <v>286</v>
+      <c r="A96" s="11">
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="12"/>
+      <c r="A97" s="11">
+        <v>176</v>
+      </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="13"/>
+      <c r="A98" s="11">
+        <v>331</v>
+      </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="13"/>
+      <c r="A99" s="11">
+        <v>124</v>
+      </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="13"/>
+      <c r="A100" s="3"/>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="13"/>
+      <c r="A101" s="12"/>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="13"/>
+      <c r="A102" s="11"/>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="13"/>
+      <c r="A103" s="3"/>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="14"/>
+      <c r="A104" s="3"/>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="13"/>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="4" t="s">
-        <v>21</v>
+      <c r="A106" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="4"/>
+      <c r="A107" s="3">
+        <v>585</v>
+      </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="15"/>
-    </row>
-    <row r="109" ht="27" spans="1:1">
-      <c r="A109" s="4" t="s">
-        <v>22</v>
+      <c r="A108" s="3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="3">
+        <v>144</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="4"/>
+      <c r="A110" s="3"/>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="4"/>
+      <c r="A111" s="5"/>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="4"/>
+      <c r="A112" s="4">
+        <v>462</v>
+      </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="6"/>
+      <c r="A113" s="5"/>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="4">
+      <c r="A114" s="3">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="3">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="3"/>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="3">
         <v>460</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="6"/>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="4">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="4">
-        <v>415</v>
-      </c>
-    </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="4"/>
+      <c r="A118" s="3"/>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="4">
-        <v>455</v>
-      </c>
+      <c r="A119" s="5"/>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="6"/>
+      <c r="A120" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="4"/>
+      <c r="A121" s="3">
+        <v>245</v>
+      </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="4" t="s">
-        <v>23</v>
+      <c r="A122" s="3">
+        <v>435</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="4"/>
+      <c r="A123" s="3">
+        <v>422</v>
+      </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="4">
-        <v>405</v>
-      </c>
+      <c r="A124" s="3"/>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A125" s="3"/>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="4">
-        <v>185</v>
-      </c>
+      <c r="A126" s="3"/>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="4" t="s">
-        <v>25</v>
+      <c r="A127" s="4">
+        <v>178</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="4"/>
+      <c r="A128" s="4">
+        <v>176</v>
+      </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="4">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="4">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="133" ht="27" spans="1:1">
-      <c r="A133" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="134" ht="27" spans="1:1">
-      <c r="A134" s="4" t="s">
-        <v>28</v>
+      <c r="A129" s="3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="130" ht="27" spans="1:1">
+      <c r="A130" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="131" ht="27" spans="1:1">
+      <c r="A131" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="132" ht="27" spans="1:1">
+      <c r="A132" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="3"/>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="4">
+        <v>465</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="4">
-        <v>1085</v>
-      </c>
+      <c r="A135" s="14"/>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="4"/>
+      <c r="A136" s="15"/>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="5"/>
+      <c r="A137" s="11">
+        <v>295</v>
+      </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="16"/>
+      <c r="A138" s="11">
+        <v>292</v>
+      </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="13"/>
+      <c r="A139" s="9"/>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="16"/>
+      <c r="A140" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="13">
-        <v>310</v>
-      </c>
+      <c r="A141" s="3"/>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="17">
-        <v>315</v>
+      <c r="A142" s="3">
+        <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="4"/>
+      <c r="A143" s="3">
+        <v>104</v>
+      </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="4">
-        <v>243</v>
-      </c>
+      <c r="A144" s="3"/>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="4"/>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="4"/>
+      <c r="A145" s="15"/>
+    </row>
+    <row r="146" ht="67.5" spans="1:1">
+      <c r="A146" s="16" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="4"/>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="16"/>
+      <c r="A147" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="148" ht="27" spans="1:1">
+      <c r="A148" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="4"/>
+      <c r="A149" s="13"/>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="18">
-        <v>513</v>
-      </c>
+      <c r="A150" s="17"/>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="4">
-        <v>61</v>
-      </c>
+      <c r="A151" s="3"/>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="15"/>
+      <c r="A152" s="18"/>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="5"/>
-    </row>
-    <row r="154" ht="27" spans="1:1">
-      <c r="A154" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="A153" s="7"/>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="13"/>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="4">
-        <v>505</v>
-      </c>
+      <c r="A155" s="19"/>
     </row>
     <row r="156" spans="1:1">
-      <c r="A156" s="4"/>
+      <c r="A156" s="18" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="15"/>
+      <c r="A157" s="14"/>
     </row>
     <row r="158" spans="1:1">
-      <c r="A158" s="4"/>
+      <c r="A158" s="3"/>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="4"/>
+      <c r="A159" s="3"/>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" s="4"/>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="19"/>
+      <c r="A160" s="11"/>
+    </row>
+    <row r="161" ht="27" spans="1:1">
+      <c r="A161" s="19" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="19"/>
+      <c r="A162" s="13"/>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="20"/>
+      <c r="A163" s="3">
+        <v>207</v>
+      </c>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="4"/>
+      <c r="A164" s="3"/>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="20" t="s">
-        <v>30</v>
-      </c>
+      <c r="A165" s="11"/>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="15"/>
+      <c r="A166" s="3"/>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="4">
-        <v>221</v>
-      </c>
+      <c r="A167" s="13"/>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="4">
-        <v>151</v>
-      </c>
+      <c r="A168" s="3"/>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="13" t="s">
-        <v>31</v>
-      </c>
+      <c r="A169" s="3"/>
     </row>
     <row r="170" spans="1:1">
-      <c r="A170" s="4"/>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="15"/>
+      <c r="A170" s="3"/>
+    </row>
+    <row r="171" ht="54" spans="1:1">
+      <c r="A171" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="172" spans="1:1">
-      <c r="A172" s="4"/>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="4"/>
+      <c r="A172" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="173" ht="40.5" spans="1:1">
+      <c r="A173" s="16" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="174" spans="1:1">
-      <c r="A174" s="4"/>
-    </row>
-    <row r="175" ht="40.5" spans="1:1">
-      <c r="A175" s="4" t="s">
-        <v>32</v>
+      <c r="A174" s="16">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="3">
+        <v>180</v>
       </c>
     </row>
     <row r="176" spans="1:1">
-      <c r="A176" s="4">
-        <v>335</v>
-      </c>
+      <c r="A176" s="3"/>
     </row>
     <row r="177" spans="1:1">
-      <c r="A177" s="18">
-        <v>327</v>
-      </c>
+      <c r="A177" s="3"/>
     </row>
     <row r="178" spans="1:1">
-      <c r="A178" s="18"/>
+      <c r="A178" s="3"/>
     </row>
     <row r="179" spans="1:1">
-      <c r="A179" s="4">
-        <v>161</v>
-      </c>
+      <c r="A179" s="3"/>
     </row>
     <row r="180" spans="1:1">
-      <c r="A180" s="4"/>
+      <c r="A180" s="3"/>
     </row>
     <row r="181" spans="1:1">
-      <c r="A181" s="4">
+      <c r="A181" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="20"/>
+    </row>
+    <row r="183" ht="40.5" spans="1:1">
+      <c r="A183" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="184" ht="40.5" spans="1:1">
+      <c r="A184" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="185" ht="40.5" spans="1:1">
+      <c r="A185" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="9"/>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="3"/>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="3"/>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="3"/>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="3">
         <v>345</v>
       </c>
     </row>
-    <row r="182" spans="1:1">
-      <c r="A182" s="4">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" s="4"/>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" s="4"/>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="186" ht="48" spans="1:1">
-      <c r="A186" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" s="4"/>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="189" ht="24" spans="1:1">
-      <c r="A189" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" s="4"/>
-    </row>
-    <row r="191" spans="1:1">
-      <c r="A191" s="10"/>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" s="4"/>
-    </row>
-    <row r="193" spans="1:1">
-      <c r="A193" s="4"/>
-    </row>
     <row r="194" spans="1:1">
-      <c r="A194" s="4"/>
+      <c r="A194" s="16"/>
     </row>
     <row r="195" spans="1:1">
-      <c r="A195" s="4">
-        <v>360</v>
-      </c>
+      <c r="A195" s="3"/>
     </row>
     <row r="196" spans="1:1">
-      <c r="A196" s="4"/>
+      <c r="A196" s="21"/>
     </row>
     <row r="197" spans="1:1">
-      <c r="A197" s="4">
-        <v>318</v>
+      <c r="A197" s="16">
+        <v>1700</v>
       </c>
     </row>
     <row r="198" spans="1:1">
-      <c r="A198" s="4" t="s">
-        <v>37</v>
+      <c r="A198" s="16">
+        <v>895</v>
       </c>
     </row>
     <row r="199" spans="1:1">
-      <c r="A199" s="4"/>
+      <c r="A199" s="16">
+        <v>1280</v>
+      </c>
     </row>
     <row r="200" spans="1:1">
-      <c r="A200" s="4"/>
+      <c r="A200" s="16">
+        <v>880</v>
+      </c>
     </row>
     <row r="201" spans="1:1">
-      <c r="A201" s="4"/>
-    </row>
-    <row r="202" spans="1:1">
-      <c r="A202" s="21"/>
-    </row>
-    <row r="203" spans="1:1">
-      <c r="A203" s="18">
-        <v>735</v>
+      <c r="A201" s="16">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="202" ht="51" spans="1:1">
+      <c r="A202" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="203" ht="54" spans="1:1">
+      <c r="A203" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="204" spans="1:1">
-      <c r="A204" s="18">
-        <v>1690</v>
+      <c r="A204" s="16">
+        <v>3330</v>
       </c>
     </row>
     <row r="205" spans="1:1">
-      <c r="A205" s="18">
-        <v>880</v>
+      <c r="A205" s="3">
+        <v>3720</v>
       </c>
     </row>
     <row r="206" spans="1:1">
-      <c r="A206" s="18">
-        <v>1280</v>
+      <c r="A206" s="3">
+        <v>1810</v>
       </c>
     </row>
     <row r="207" spans="1:1">
-      <c r="A207" s="18">
-        <v>830</v>
+      <c r="A207" s="3">
+        <v>955</v>
       </c>
     </row>
     <row r="208" spans="1:1">
-      <c r="A208" s="18">
-        <v>1060</v>
+      <c r="A208" s="3">
+        <v>2110</v>
       </c>
     </row>
     <row r="209" spans="1:1">
-      <c r="A209" s="18">
-        <v>1855</v>
+      <c r="A209" s="16">
+        <v>768</v>
       </c>
     </row>
     <row r="210" spans="1:1">
-      <c r="A210" s="18">
-        <v>2040</v>
+      <c r="A210" s="16">
+        <v>710</v>
       </c>
     </row>
     <row r="211" spans="1:1">
-      <c r="A211" s="10">
-        <v>2480</v>
-      </c>
+      <c r="A211" s="3"/>
     </row>
     <row r="212" spans="1:1">
-      <c r="A212" s="22">
-        <v>3450</v>
+      <c r="A212" s="3">
+        <v>1640</v>
       </c>
     </row>
     <row r="213" spans="1:1">
-      <c r="A213" s="22">
-        <v>3720</v>
+      <c r="A213" s="16">
+        <v>1030</v>
       </c>
     </row>
     <row r="214" spans="1:1">
-      <c r="A214" s="12"/>
-    </row>
-    <row r="215" ht="24" spans="1:1">
-      <c r="A215" s="23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="216" ht="24" spans="1:1">
-      <c r="A216" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="217" ht="24" spans="1:1">
-      <c r="A217" s="23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="218" ht="24" spans="1:1">
-      <c r="A218" s="23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="219" ht="24" spans="1:1">
-      <c r="A219" s="23" t="s">
-        <v>42</v>
+      <c r="A214" s="16">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="22"/>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="3">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="3">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="3">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="3">
+        <v>1264</v>
       </c>
     </row>
     <row r="220" spans="1:1">
-      <c r="A220" s="22"/>
+      <c r="A220" s="3">
+        <v>1058</v>
+      </c>
     </row>
     <row r="221" spans="1:1">
-      <c r="A221" s="22"/>
+      <c r="A221" s="23">
+        <v>540</v>
+      </c>
     </row>
     <row r="222" spans="1:1">
-      <c r="A222" s="12"/>
+      <c r="A222" s="3">
+        <v>743</v>
+      </c>
     </row>
     <row r="223" spans="1:1">
-      <c r="A223" s="3"/>
+      <c r="A223" s="23">
+        <v>1184</v>
+      </c>
     </row>
     <row r="224" spans="1:1">
-      <c r="A224" s="10"/>
+      <c r="A224" s="22"/>
     </row>
     <row r="225" spans="1:1">
-      <c r="A225" s="24"/>
+      <c r="A225" s="3"/>
     </row>
     <row r="226" spans="1:1">
-      <c r="A226" s="25">
-        <v>3410</v>
-      </c>
+      <c r="A226" s="3"/>
     </row>
     <row r="227" spans="1:1">
-      <c r="A227" s="26">
-        <v>3610</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" s="25">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1">
-      <c r="A229" s="25">
-        <v>1840</v>
+      <c r="A227" s="12"/>
+    </row>
+    <row r="228" ht="36" spans="1:1">
+      <c r="A228" s="20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="229" ht="36" spans="1:1">
+      <c r="A229" s="20" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="230" spans="1:1">
-      <c r="A230" s="27">
-        <v>1700</v>
+      <c r="A230" s="3">
+        <v>1790</v>
       </c>
     </row>
     <row r="231" spans="1:1">
-      <c r="A231" s="27">
-        <v>1800</v>
+      <c r="A231" s="3">
+        <v>1920</v>
       </c>
     </row>
     <row r="232" spans="1:1">
-      <c r="A232" s="14"/>
+      <c r="A232" s="3">
+        <v>1750</v>
+      </c>
     </row>
     <row r="233" spans="1:1">
-      <c r="A233" s="13">
-        <v>3070</v>
+      <c r="A233" s="3">
+        <v>1820</v>
       </c>
     </row>
     <row r="234" spans="1:1">
-      <c r="A234" s="13">
-        <v>2710</v>
-      </c>
+      <c r="A234" s="12"/>
     </row>
     <row r="235" spans="1:1">
-      <c r="A235" s="13">
-        <v>2700</v>
+      <c r="A235" s="11">
+        <v>3600</v>
       </c>
     </row>
     <row r="236" spans="1:1">
-      <c r="A236" s="13">
-        <v>2200</v>
+      <c r="A236" s="11">
+        <v>3400</v>
       </c>
     </row>
     <row r="237" spans="1:1">
-      <c r="A237" s="13">
-        <v>3130</v>
+      <c r="A237" s="11">
+        <v>3100</v>
       </c>
     </row>
     <row r="238" spans="1:1">
-      <c r="A238" s="13">
-        <v>2700</v>
-      </c>
-    </row>
-    <row r="239" ht="27" spans="1:1">
-      <c r="A239" s="13" t="s">
-        <v>43</v>
+      <c r="A238" s="11">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="11">
+        <v>3620</v>
       </c>
     </row>
     <row r="240" spans="1:1">
-      <c r="A240" s="14"/>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" s="13">
-        <v>2150</v>
+      <c r="A240" s="11">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="241" ht="27" spans="1:1">
+      <c r="A241" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="242" spans="1:1">
-      <c r="A242" s="13">
-        <v>2200</v>
-      </c>
+      <c r="A242" s="12"/>
     </row>
     <row r="243" spans="1:1">
-      <c r="A243" s="28">
+      <c r="A243" s="11">
         <v>2300</v>
       </c>
     </row>
     <row r="244" spans="1:1">
-      <c r="A244" s="28">
-        <v>2600</v>
+      <c r="A244" s="11">
+        <v>2300</v>
       </c>
     </row>
     <row r="245" spans="1:1">
-      <c r="A245" s="28">
-        <v>2920</v>
-      </c>
-    </row>
-    <row r="246" ht="27" spans="1:1">
-      <c r="A246" s="13" t="s">
-        <v>44</v>
+      <c r="A245" s="24">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="24">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="24">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="248" ht="27" spans="1:1">
+      <c r="A248" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
